--- a/.schema/MSY_KADOBI.xlsx
+++ b/.schema/MSY_KADOBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9FD0C4-6545-48CC-B75F-3FA1ECF7CB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18D5F47-7C2F-4717-8786-C551EDD8F4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{85859E91-B151-45F1-A30C-1C61CD1AC1FE}"/>
   </bookViews>
@@ -69,8 +69,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="177" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
-    <numFmt numFmtId="179" formatCode="yyyymmdd"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
+    <numFmt numFmtId="179" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -165,7 +165,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -544,14 +544,14 @@
       <c r="D3" s="4"/>
       <c r="E3" s="5">
         <f ca="1">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
       </c>
       <c r="G3" s="5">
         <f ca="1">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
@@ -572,14 +572,14 @@
       <c r="D4" s="4"/>
       <c r="E4" s="5">
         <f t="shared" ref="E4:E67" ca="1" si="1">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" ref="G4:G67" ca="1" si="2">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H4" s="4">
         <v>0</v>
@@ -600,14 +600,14 @@
       <c r="D5" s="4"/>
       <c r="E5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
@@ -628,14 +628,14 @@
       <c r="D6" s="4"/>
       <c r="E6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H6" s="4">
         <v>0</v>
@@ -656,14 +656,14 @@
       <c r="D7" s="4"/>
       <c r="E7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
@@ -684,14 +684,14 @@
       <c r="D8" s="4"/>
       <c r="E8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
@@ -712,14 +712,14 @@
       <c r="D9" s="4"/>
       <c r="E9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -740,14 +740,14 @@
       <c r="D10" s="4"/>
       <c r="E10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
@@ -768,14 +768,14 @@
       <c r="D11" s="4"/>
       <c r="E11" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H11" s="4">
         <v>0</v>
@@ -796,14 +796,14 @@
       <c r="D12" s="4"/>
       <c r="E12" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
@@ -824,14 +824,14 @@
       <c r="D13" s="4"/>
       <c r="E13" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H13" s="4">
         <v>0</v>
@@ -852,14 +852,14 @@
       <c r="D14" s="4"/>
       <c r="E14" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H14" s="4">
         <v>0</v>
@@ -880,14 +880,14 @@
       <c r="D15" s="4"/>
       <c r="E15" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H15" s="4">
         <v>0</v>
@@ -908,14 +908,14 @@
       <c r="D16" s="4"/>
       <c r="E16" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F16" s="4">
         <v>0</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H16" s="4">
         <v>0</v>
@@ -936,14 +936,14 @@
       <c r="D17" s="4"/>
       <c r="E17" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H17" s="4">
         <v>0</v>
@@ -964,14 +964,14 @@
       <c r="D18" s="4"/>
       <c r="E18" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F18" s="4">
         <v>0</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H18" s="4">
         <v>0</v>
@@ -992,14 +992,14 @@
       <c r="D19" s="4"/>
       <c r="E19" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F19" s="4">
         <v>0</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H19" s="4">
         <v>0</v>
@@ -1020,14 +1020,14 @@
       <c r="D20" s="4"/>
       <c r="E20" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F20" s="4">
         <v>0</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H20" s="4">
         <v>0</v>
@@ -1048,14 +1048,14 @@
       <c r="D21" s="4"/>
       <c r="E21" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F21" s="4">
         <v>0</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H21" s="4">
         <v>0</v>
@@ -1076,14 +1076,14 @@
       <c r="D22" s="4"/>
       <c r="E22" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F22" s="4">
         <v>0</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H22" s="4">
         <v>0</v>
@@ -1104,14 +1104,14 @@
       <c r="D23" s="4"/>
       <c r="E23" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F23" s="4">
         <v>0</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H23" s="4">
         <v>0</v>
@@ -1132,14 +1132,14 @@
       <c r="D24" s="4"/>
       <c r="E24" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F24" s="4">
         <v>0</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H24" s="4">
         <v>0</v>
@@ -1160,14 +1160,14 @@
       <c r="D25" s="4"/>
       <c r="E25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F25" s="4">
         <v>0</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H25" s="4">
         <v>0</v>
@@ -1188,14 +1188,14 @@
       <c r="D26" s="4"/>
       <c r="E26" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F26" s="4">
         <v>0</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H26" s="4">
         <v>0</v>
@@ -1216,14 +1216,14 @@
       <c r="D27" s="4"/>
       <c r="E27" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F27" s="4">
         <v>0</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H27" s="4">
         <v>0</v>
@@ -1244,14 +1244,14 @@
       <c r="D28" s="4"/>
       <c r="E28" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H28" s="4">
         <v>0</v>
@@ -1272,14 +1272,14 @@
       <c r="D29" s="4"/>
       <c r="E29" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F29" s="4">
         <v>0</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H29" s="4">
         <v>0</v>
@@ -1300,14 +1300,14 @@
       <c r="D30" s="4"/>
       <c r="E30" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H30" s="4">
         <v>0</v>
@@ -1328,14 +1328,14 @@
       <c r="D31" s="4"/>
       <c r="E31" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F31" s="4">
         <v>0</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H31" s="4">
         <v>0</v>
@@ -1356,14 +1356,14 @@
       <c r="D32" s="4"/>
       <c r="E32" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F32" s="4">
         <v>0</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H32" s="4">
         <v>0</v>
@@ -1384,14 +1384,14 @@
       <c r="D33" s="4"/>
       <c r="E33" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F33" s="4">
         <v>0</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H33" s="4">
         <v>0</v>
@@ -1412,14 +1412,14 @@
       <c r="D34" s="4"/>
       <c r="E34" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F34" s="4">
         <v>0</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H34" s="4">
         <v>0</v>
@@ -1440,14 +1440,14 @@
       <c r="D35" s="4"/>
       <c r="E35" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F35" s="4">
         <v>0</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H35" s="4">
         <v>0</v>
@@ -1468,14 +1468,14 @@
       <c r="D36" s="4"/>
       <c r="E36" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F36" s="4">
         <v>0</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H36" s="4">
         <v>0</v>
@@ -1496,14 +1496,14 @@
       <c r="D37" s="4"/>
       <c r="E37" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F37" s="4">
         <v>0</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H37" s="4">
         <v>0</v>
@@ -1524,14 +1524,14 @@
       <c r="D38" s="4"/>
       <c r="E38" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F38" s="4">
         <v>0</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H38" s="4">
         <v>0</v>
@@ -1552,14 +1552,14 @@
       <c r="D39" s="4"/>
       <c r="E39" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F39" s="4">
         <v>0</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H39" s="4">
         <v>0</v>
@@ -1580,14 +1580,14 @@
       <c r="D40" s="4"/>
       <c r="E40" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F40" s="4">
         <v>0</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H40" s="4">
         <v>0</v>
@@ -1608,14 +1608,14 @@
       <c r="D41" s="4"/>
       <c r="E41" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F41" s="4">
         <v>0</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H41" s="4">
         <v>0</v>
@@ -1636,14 +1636,14 @@
       <c r="D42" s="4"/>
       <c r="E42" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F42" s="4">
         <v>0</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H42" s="4">
         <v>0</v>
@@ -1664,14 +1664,14 @@
       <c r="D43" s="4"/>
       <c r="E43" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F43" s="4">
         <v>0</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H43" s="4">
         <v>0</v>
@@ -1692,14 +1692,14 @@
       <c r="D44" s="4"/>
       <c r="E44" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F44" s="4">
         <v>0</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H44" s="4">
         <v>0</v>
@@ -1720,14 +1720,14 @@
       <c r="D45" s="4"/>
       <c r="E45" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F45" s="4">
         <v>0</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H45" s="4">
         <v>0</v>
@@ -1748,14 +1748,14 @@
       <c r="D46" s="4"/>
       <c r="E46" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F46" s="4">
         <v>0</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H46" s="4">
         <v>0</v>
@@ -1776,14 +1776,14 @@
       <c r="D47" s="4"/>
       <c r="E47" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F47" s="4">
         <v>0</v>
       </c>
       <c r="G47" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H47" s="4">
         <v>0</v>
@@ -1804,14 +1804,14 @@
       <c r="D48" s="4"/>
       <c r="E48" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F48" s="4">
         <v>0</v>
       </c>
       <c r="G48" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H48" s="4">
         <v>0</v>
@@ -1832,14 +1832,14 @@
       <c r="D49" s="4"/>
       <c r="E49" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F49" s="4">
         <v>0</v>
       </c>
       <c r="G49" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H49" s="4">
         <v>0</v>
@@ -1860,14 +1860,14 @@
       <c r="D50" s="4"/>
       <c r="E50" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F50" s="4">
         <v>0</v>
       </c>
       <c r="G50" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H50" s="4">
         <v>0</v>
@@ -1888,14 +1888,14 @@
       <c r="D51" s="4"/>
       <c r="E51" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F51" s="4">
         <v>0</v>
       </c>
       <c r="G51" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H51" s="4">
         <v>0</v>
@@ -1916,14 +1916,14 @@
       <c r="D52" s="4"/>
       <c r="E52" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F52" s="4">
         <v>0</v>
       </c>
       <c r="G52" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H52" s="4">
         <v>0</v>
@@ -1944,14 +1944,14 @@
       <c r="D53" s="4"/>
       <c r="E53" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F53" s="4">
         <v>0</v>
       </c>
       <c r="G53" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H53" s="4">
         <v>0</v>
@@ -1972,14 +1972,14 @@
       <c r="D54" s="4"/>
       <c r="E54" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F54" s="4">
         <v>0</v>
       </c>
       <c r="G54" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H54" s="4">
         <v>0</v>
@@ -2000,14 +2000,14 @@
       <c r="D55" s="4"/>
       <c r="E55" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F55" s="4">
         <v>0</v>
       </c>
       <c r="G55" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H55" s="4">
         <v>0</v>
@@ -2028,14 +2028,14 @@
       <c r="D56" s="4"/>
       <c r="E56" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F56" s="4">
         <v>0</v>
       </c>
       <c r="G56" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H56" s="4">
         <v>0</v>
@@ -2056,14 +2056,14 @@
       <c r="D57" s="4"/>
       <c r="E57" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F57" s="4">
         <v>0</v>
       </c>
       <c r="G57" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H57" s="4">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       <c r="D58" s="4"/>
       <c r="E58" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F58" s="4">
         <v>0</v>
       </c>
       <c r="G58" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H58" s="4">
         <v>0</v>
@@ -2112,14 +2112,14 @@
       <c r="D59" s="4"/>
       <c r="E59" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F59" s="4">
         <v>0</v>
       </c>
       <c r="G59" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H59" s="4">
         <v>0</v>
@@ -2140,14 +2140,14 @@
       <c r="D60" s="4"/>
       <c r="E60" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F60" s="4">
         <v>0</v>
       </c>
       <c r="G60" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H60" s="4">
         <v>0</v>
@@ -2168,14 +2168,14 @@
       <c r="D61" s="4"/>
       <c r="E61" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F61" s="4">
         <v>0</v>
       </c>
       <c r="G61" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H61" s="4">
         <v>0</v>
@@ -2196,14 +2196,14 @@
       <c r="D62" s="4"/>
       <c r="E62" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F62" s="4">
         <v>0</v>
       </c>
       <c r="G62" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H62" s="4">
         <v>0</v>
@@ -2224,14 +2224,14 @@
       <c r="D63" s="4"/>
       <c r="E63" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F63" s="4">
         <v>0</v>
       </c>
       <c r="G63" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H63" s="4">
         <v>0</v>
@@ -2252,14 +2252,14 @@
       <c r="D64" s="4"/>
       <c r="E64" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F64" s="4">
         <v>0</v>
       </c>
       <c r="G64" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H64" s="4">
         <v>0</v>
@@ -2280,14 +2280,14 @@
       <c r="D65" s="4"/>
       <c r="E65" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F65" s="4">
         <v>0</v>
       </c>
       <c r="G65" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H65" s="4">
         <v>0</v>
@@ -2308,14 +2308,14 @@
       <c r="D66" s="4"/>
       <c r="E66" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F66" s="4">
         <v>0</v>
       </c>
       <c r="G66" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H66" s="4">
         <v>0</v>
@@ -2336,14 +2336,14 @@
       <c r="D67" s="4"/>
       <c r="E67" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F67" s="4">
         <v>0</v>
       </c>
       <c r="G67" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H67" s="4">
         <v>0</v>
@@ -2364,14 +2364,14 @@
       <c r="D68" s="4"/>
       <c r="E68" s="5">
         <f t="shared" ref="E68:E131" ca="1" si="8">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F68" s="4">
         <v>0</v>
       </c>
       <c r="G68" s="5">
         <f t="shared" ref="G68:G131" ca="1" si="9">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H68" s="4">
         <v>0</v>
@@ -2392,14 +2392,14 @@
       <c r="D69" s="4"/>
       <c r="E69" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F69" s="4">
         <v>0</v>
       </c>
       <c r="G69" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H69" s="4">
         <v>0</v>
@@ -2420,14 +2420,14 @@
       <c r="D70" s="4"/>
       <c r="E70" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F70" s="4">
         <v>0</v>
       </c>
       <c r="G70" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H70" s="4">
         <v>0</v>
@@ -2448,14 +2448,14 @@
       <c r="D71" s="4"/>
       <c r="E71" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F71" s="4">
         <v>0</v>
       </c>
       <c r="G71" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H71" s="4">
         <v>0</v>
@@ -2476,14 +2476,14 @@
       <c r="D72" s="4"/>
       <c r="E72" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F72" s="4">
         <v>0</v>
       </c>
       <c r="G72" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H72" s="4">
         <v>0</v>
@@ -2504,14 +2504,14 @@
       <c r="D73" s="4"/>
       <c r="E73" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F73" s="4">
         <v>0</v>
       </c>
       <c r="G73" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H73" s="4">
         <v>0</v>
@@ -2532,14 +2532,14 @@
       <c r="D74" s="4"/>
       <c r="E74" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F74" s="4">
         <v>0</v>
       </c>
       <c r="G74" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H74" s="4">
         <v>0</v>
@@ -2560,14 +2560,14 @@
       <c r="D75" s="4"/>
       <c r="E75" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F75" s="4">
         <v>0</v>
       </c>
       <c r="G75" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H75" s="4">
         <v>0</v>
@@ -2588,14 +2588,14 @@
       <c r="D76" s="4"/>
       <c r="E76" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F76" s="4">
         <v>0</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H76" s="4">
         <v>0</v>
@@ -2616,14 +2616,14 @@
       <c r="D77" s="4"/>
       <c r="E77" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F77" s="4">
         <v>0</v>
       </c>
       <c r="G77" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H77" s="4">
         <v>0</v>
@@ -2644,14 +2644,14 @@
       <c r="D78" s="4"/>
       <c r="E78" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F78" s="4">
         <v>0</v>
       </c>
       <c r="G78" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H78" s="4">
         <v>0</v>
@@ -2672,14 +2672,14 @@
       <c r="D79" s="4"/>
       <c r="E79" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F79" s="4">
         <v>0</v>
       </c>
       <c r="G79" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H79" s="4">
         <v>0</v>
@@ -2700,14 +2700,14 @@
       <c r="D80" s="4"/>
       <c r="E80" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F80" s="4">
         <v>0</v>
       </c>
       <c r="G80" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H80" s="4">
         <v>0</v>
@@ -2728,14 +2728,14 @@
       <c r="D81" s="4"/>
       <c r="E81" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F81" s="4">
         <v>0</v>
       </c>
       <c r="G81" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H81" s="4">
         <v>0</v>
@@ -2756,14 +2756,14 @@
       <c r="D82" s="4"/>
       <c r="E82" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F82" s="4">
         <v>0</v>
       </c>
       <c r="G82" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H82" s="4">
         <v>0</v>
@@ -2784,14 +2784,14 @@
       <c r="D83" s="4"/>
       <c r="E83" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F83" s="4">
         <v>0</v>
       </c>
       <c r="G83" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H83" s="4">
         <v>0</v>
@@ -2812,14 +2812,14 @@
       <c r="D84" s="4"/>
       <c r="E84" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F84" s="4">
         <v>0</v>
       </c>
       <c r="G84" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H84" s="4">
         <v>0</v>
@@ -2840,14 +2840,14 @@
       <c r="D85" s="4"/>
       <c r="E85" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F85" s="4">
         <v>0</v>
       </c>
       <c r="G85" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H85" s="4">
         <v>0</v>
@@ -2868,14 +2868,14 @@
       <c r="D86" s="4"/>
       <c r="E86" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F86" s="4">
         <v>0</v>
       </c>
       <c r="G86" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H86" s="4">
         <v>0</v>
@@ -2896,14 +2896,14 @@
       <c r="D87" s="4"/>
       <c r="E87" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F87" s="4">
         <v>0</v>
       </c>
       <c r="G87" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H87" s="4">
         <v>0</v>
@@ -2924,14 +2924,14 @@
       <c r="D88" s="4"/>
       <c r="E88" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F88" s="4">
         <v>0</v>
       </c>
       <c r="G88" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H88" s="4">
         <v>0</v>
@@ -2952,14 +2952,14 @@
       <c r="D89" s="4"/>
       <c r="E89" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F89" s="4">
         <v>0</v>
       </c>
       <c r="G89" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H89" s="4">
         <v>0</v>
@@ -2980,14 +2980,14 @@
       <c r="D90" s="4"/>
       <c r="E90" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F90" s="4">
         <v>0</v>
       </c>
       <c r="G90" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H90" s="4">
         <v>0</v>
@@ -3008,14 +3008,14 @@
       <c r="D91" s="4"/>
       <c r="E91" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F91" s="4">
         <v>0</v>
       </c>
       <c r="G91" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H91" s="4">
         <v>0</v>
@@ -3036,14 +3036,14 @@
       <c r="D92" s="4"/>
       <c r="E92" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F92" s="4">
         <v>0</v>
       </c>
       <c r="G92" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H92" s="4">
         <v>0</v>
@@ -3064,14 +3064,14 @@
       <c r="D93" s="4"/>
       <c r="E93" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F93" s="4">
         <v>0</v>
       </c>
       <c r="G93" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H93" s="4">
         <v>0</v>
@@ -3092,14 +3092,14 @@
       <c r="D94" s="4"/>
       <c r="E94" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F94" s="4">
         <v>0</v>
       </c>
       <c r="G94" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H94" s="4">
         <v>0</v>
@@ -3120,14 +3120,14 @@
       <c r="D95" s="4"/>
       <c r="E95" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F95" s="4">
         <v>0</v>
       </c>
       <c r="G95" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H95" s="4">
         <v>0</v>
@@ -3148,14 +3148,14 @@
       <c r="D96" s="4"/>
       <c r="E96" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F96" s="4">
         <v>0</v>
       </c>
       <c r="G96" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H96" s="4">
         <v>0</v>
@@ -3176,14 +3176,14 @@
       <c r="D97" s="4"/>
       <c r="E97" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F97" s="4">
         <v>0</v>
       </c>
       <c r="G97" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H97" s="4">
         <v>0</v>
@@ -3204,14 +3204,14 @@
       <c r="D98" s="4"/>
       <c r="E98" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F98" s="4">
         <v>0</v>
       </c>
       <c r="G98" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H98" s="4">
         <v>0</v>
@@ -3232,14 +3232,14 @@
       <c r="D99" s="4"/>
       <c r="E99" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F99" s="4">
         <v>0</v>
       </c>
       <c r="G99" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H99" s="4">
         <v>0</v>
@@ -3260,14 +3260,14 @@
       <c r="D100" s="4"/>
       <c r="E100" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F100" s="4">
         <v>0</v>
       </c>
       <c r="G100" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H100" s="4">
         <v>0</v>
@@ -3288,14 +3288,14 @@
       <c r="D101" s="4"/>
       <c r="E101" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F101" s="4">
         <v>0</v>
       </c>
       <c r="G101" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H101" s="4">
         <v>0</v>
@@ -3316,14 +3316,14 @@
       <c r="D102" s="4"/>
       <c r="E102" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F102" s="4">
         <v>0</v>
       </c>
       <c r="G102" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H102" s="4">
         <v>0</v>
@@ -3344,14 +3344,14 @@
       <c r="D103" s="4"/>
       <c r="E103" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F103" s="4">
         <v>0</v>
       </c>
       <c r="G103" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H103" s="4">
         <v>0</v>
@@ -3372,14 +3372,14 @@
       <c r="D104" s="4"/>
       <c r="E104" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F104" s="4">
         <v>0</v>
       </c>
       <c r="G104" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H104" s="4">
         <v>0</v>
@@ -3400,14 +3400,14 @@
       <c r="D105" s="4"/>
       <c r="E105" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F105" s="4">
         <v>0</v>
       </c>
       <c r="G105" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H105" s="4">
         <v>0</v>
@@ -3428,14 +3428,14 @@
       <c r="D106" s="4"/>
       <c r="E106" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F106" s="4">
         <v>0</v>
       </c>
       <c r="G106" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H106" s="4">
         <v>0</v>
@@ -3456,14 +3456,14 @@
       <c r="D107" s="4"/>
       <c r="E107" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F107" s="4">
         <v>0</v>
       </c>
       <c r="G107" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H107" s="4">
         <v>0</v>
@@ -3484,14 +3484,14 @@
       <c r="D108" s="4"/>
       <c r="E108" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F108" s="4">
         <v>0</v>
       </c>
       <c r="G108" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H108" s="4">
         <v>0</v>
@@ -3512,14 +3512,14 @@
       <c r="D109" s="4"/>
       <c r="E109" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F109" s="4">
         <v>0</v>
       </c>
       <c r="G109" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H109" s="4">
         <v>0</v>
@@ -3540,14 +3540,14 @@
       <c r="D110" s="4"/>
       <c r="E110" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F110" s="4">
         <v>0</v>
       </c>
       <c r="G110" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H110" s="4">
         <v>0</v>
@@ -3568,14 +3568,14 @@
       <c r="D111" s="4"/>
       <c r="E111" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F111" s="4">
         <v>0</v>
       </c>
       <c r="G111" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H111" s="4">
         <v>0</v>
@@ -3596,14 +3596,14 @@
       <c r="D112" s="4"/>
       <c r="E112" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F112" s="4">
         <v>0</v>
       </c>
       <c r="G112" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H112" s="4">
         <v>0</v>
@@ -3624,14 +3624,14 @@
       <c r="D113" s="4"/>
       <c r="E113" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F113" s="4">
         <v>0</v>
       </c>
       <c r="G113" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H113" s="4">
         <v>0</v>
@@ -3652,14 +3652,14 @@
       <c r="D114" s="4"/>
       <c r="E114" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F114" s="4">
         <v>0</v>
       </c>
       <c r="G114" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H114" s="4">
         <v>0</v>
@@ -3680,14 +3680,14 @@
       <c r="D115" s="4"/>
       <c r="E115" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F115" s="4">
         <v>0</v>
       </c>
       <c r="G115" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H115" s="4">
         <v>0</v>
@@ -3708,14 +3708,14 @@
       <c r="D116" s="4"/>
       <c r="E116" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F116" s="4">
         <v>0</v>
       </c>
       <c r="G116" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H116" s="4">
         <v>0</v>
@@ -3736,14 +3736,14 @@
       <c r="D117" s="4"/>
       <c r="E117" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F117" s="4">
         <v>0</v>
       </c>
       <c r="G117" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H117" s="4">
         <v>0</v>
@@ -3764,14 +3764,14 @@
       <c r="D118" s="4"/>
       <c r="E118" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F118" s="4">
         <v>0</v>
       </c>
       <c r="G118" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H118" s="4">
         <v>0</v>
@@ -3792,14 +3792,14 @@
       <c r="D119" s="4"/>
       <c r="E119" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F119" s="4">
         <v>0</v>
       </c>
       <c r="G119" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H119" s="4">
         <v>0</v>
@@ -3820,14 +3820,14 @@
       <c r="D120" s="4"/>
       <c r="E120" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F120" s="4">
         <v>0</v>
       </c>
       <c r="G120" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H120" s="4">
         <v>0</v>
@@ -3848,14 +3848,14 @@
       <c r="D121" s="4"/>
       <c r="E121" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F121" s="4">
         <v>0</v>
       </c>
       <c r="G121" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H121" s="4">
         <v>0</v>
@@ -3876,14 +3876,14 @@
       <c r="D122" s="4"/>
       <c r="E122" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F122" s="4">
         <v>0</v>
       </c>
       <c r="G122" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H122" s="4">
         <v>0</v>
@@ -3904,14 +3904,14 @@
       <c r="D123" s="4"/>
       <c r="E123" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F123" s="4">
         <v>0</v>
       </c>
       <c r="G123" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H123" s="4">
         <v>0</v>
@@ -3932,14 +3932,14 @@
       <c r="D124" s="4"/>
       <c r="E124" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F124" s="4">
         <v>0</v>
       </c>
       <c r="G124" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H124" s="4">
         <v>0</v>
@@ -3960,14 +3960,14 @@
       <c r="D125" s="4"/>
       <c r="E125" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F125" s="4">
         <v>0</v>
       </c>
       <c r="G125" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H125" s="4">
         <v>0</v>
@@ -3988,14 +3988,14 @@
       <c r="D126" s="4"/>
       <c r="E126" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F126" s="4">
         <v>0</v>
       </c>
       <c r="G126" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H126" s="4">
         <v>0</v>
@@ -4016,14 +4016,14 @@
       <c r="D127" s="4"/>
       <c r="E127" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F127" s="4">
         <v>0</v>
       </c>
       <c r="G127" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H127" s="4">
         <v>0</v>
@@ -4044,14 +4044,14 @@
       <c r="D128" s="4"/>
       <c r="E128" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F128" s="4">
         <v>0</v>
       </c>
       <c r="G128" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H128" s="4">
         <v>0</v>
@@ -4072,14 +4072,14 @@
       <c r="D129" s="4"/>
       <c r="E129" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F129" s="4">
         <v>0</v>
       </c>
       <c r="G129" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H129" s="4">
         <v>0</v>
@@ -4100,14 +4100,14 @@
       <c r="D130" s="4"/>
       <c r="E130" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F130" s="4">
         <v>0</v>
       </c>
       <c r="G130" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H130" s="4">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       <c r="D131" s="4"/>
       <c r="E131" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F131" s="4">
         <v>0</v>
       </c>
       <c r="G131" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H131" s="4">
         <v>0</v>
@@ -4156,14 +4156,14 @@
       <c r="D132" s="4"/>
       <c r="E132" s="5">
         <f t="shared" ref="E132:E195" ca="1" si="14">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F132" s="4">
         <v>0</v>
       </c>
       <c r="G132" s="5">
         <f t="shared" ref="G132:G195" ca="1" si="15">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H132" s="4">
         <v>0</v>
@@ -4184,14 +4184,14 @@
       <c r="D133" s="4"/>
       <c r="E133" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F133" s="4">
         <v>0</v>
       </c>
       <c r="G133" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H133" s="4">
         <v>0</v>
@@ -4212,14 +4212,14 @@
       <c r="D134" s="4"/>
       <c r="E134" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F134" s="4">
         <v>0</v>
       </c>
       <c r="G134" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H134" s="4">
         <v>0</v>
@@ -4240,14 +4240,14 @@
       <c r="D135" s="4"/>
       <c r="E135" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F135" s="4">
         <v>0</v>
       </c>
       <c r="G135" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H135" s="4">
         <v>0</v>
@@ -4268,14 +4268,14 @@
       <c r="D136" s="4"/>
       <c r="E136" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F136" s="4">
         <v>0</v>
       </c>
       <c r="G136" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H136" s="4">
         <v>0</v>
@@ -4296,14 +4296,14 @@
       <c r="D137" s="4"/>
       <c r="E137" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F137" s="4">
         <v>0</v>
       </c>
       <c r="G137" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H137" s="4">
         <v>0</v>
@@ -4324,14 +4324,14 @@
       <c r="D138" s="4"/>
       <c r="E138" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F138" s="4">
         <v>0</v>
       </c>
       <c r="G138" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H138" s="4">
         <v>0</v>
@@ -4352,14 +4352,14 @@
       <c r="D139" s="4"/>
       <c r="E139" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F139" s="4">
         <v>0</v>
       </c>
       <c r="G139" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H139" s="4">
         <v>0</v>
@@ -4380,14 +4380,14 @@
       <c r="D140" s="4"/>
       <c r="E140" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F140" s="4">
         <v>0</v>
       </c>
       <c r="G140" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H140" s="4">
         <v>0</v>
@@ -4408,14 +4408,14 @@
       <c r="D141" s="4"/>
       <c r="E141" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F141" s="4">
         <v>0</v>
       </c>
       <c r="G141" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H141" s="4">
         <v>0</v>
@@ -4436,14 +4436,14 @@
       <c r="D142" s="4"/>
       <c r="E142" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F142" s="4">
         <v>0</v>
       </c>
       <c r="G142" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H142" s="4">
         <v>0</v>
@@ -4464,14 +4464,14 @@
       <c r="D143" s="4"/>
       <c r="E143" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F143" s="4">
         <v>0</v>
       </c>
       <c r="G143" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H143" s="4">
         <v>0</v>
@@ -4492,14 +4492,14 @@
       <c r="D144" s="4"/>
       <c r="E144" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F144" s="4">
         <v>0</v>
       </c>
       <c r="G144" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H144" s="4">
         <v>0</v>
@@ -4520,14 +4520,14 @@
       <c r="D145" s="4"/>
       <c r="E145" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F145" s="4">
         <v>0</v>
       </c>
       <c r="G145" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H145" s="4">
         <v>0</v>
@@ -4548,14 +4548,14 @@
       <c r="D146" s="4"/>
       <c r="E146" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F146" s="4">
         <v>0</v>
       </c>
       <c r="G146" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H146" s="4">
         <v>0</v>
@@ -4576,14 +4576,14 @@
       <c r="D147" s="4"/>
       <c r="E147" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F147" s="4">
         <v>0</v>
       </c>
       <c r="G147" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H147" s="4">
         <v>0</v>
@@ -4604,14 +4604,14 @@
       <c r="D148" s="4"/>
       <c r="E148" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F148" s="4">
         <v>0</v>
       </c>
       <c r="G148" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H148" s="4">
         <v>0</v>
@@ -4632,14 +4632,14 @@
       <c r="D149" s="4"/>
       <c r="E149" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F149" s="4">
         <v>0</v>
       </c>
       <c r="G149" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H149" s="4">
         <v>0</v>
@@ -4660,14 +4660,14 @@
       <c r="D150" s="4"/>
       <c r="E150" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F150" s="4">
         <v>0</v>
       </c>
       <c r="G150" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H150" s="4">
         <v>0</v>
@@ -4688,14 +4688,14 @@
       <c r="D151" s="4"/>
       <c r="E151" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F151" s="4">
         <v>0</v>
       </c>
       <c r="G151" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H151" s="4">
         <v>0</v>
@@ -4716,14 +4716,14 @@
       <c r="D152" s="4"/>
       <c r="E152" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F152" s="4">
         <v>0</v>
       </c>
       <c r="G152" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H152" s="4">
         <v>0</v>
@@ -4744,14 +4744,14 @@
       <c r="D153" s="4"/>
       <c r="E153" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F153" s="4">
         <v>0</v>
       </c>
       <c r="G153" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H153" s="4">
         <v>0</v>
@@ -4772,14 +4772,14 @@
       <c r="D154" s="4"/>
       <c r="E154" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F154" s="4">
         <v>0</v>
       </c>
       <c r="G154" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H154" s="4">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       <c r="D155" s="4"/>
       <c r="E155" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F155" s="4">
         <v>0</v>
       </c>
       <c r="G155" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H155" s="4">
         <v>0</v>
@@ -4828,14 +4828,14 @@
       <c r="D156" s="4"/>
       <c r="E156" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F156" s="4">
         <v>0</v>
       </c>
       <c r="G156" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H156" s="4">
         <v>0</v>
@@ -4856,14 +4856,14 @@
       <c r="D157" s="4"/>
       <c r="E157" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F157" s="4">
         <v>0</v>
       </c>
       <c r="G157" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H157" s="4">
         <v>0</v>
@@ -4884,14 +4884,14 @@
       <c r="D158" s="4"/>
       <c r="E158" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F158" s="4">
         <v>0</v>
       </c>
       <c r="G158" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H158" s="4">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       <c r="D159" s="4"/>
       <c r="E159" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F159" s="4">
         <v>0</v>
       </c>
       <c r="G159" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H159" s="4">
         <v>0</v>
@@ -4940,14 +4940,14 @@
       <c r="D160" s="4"/>
       <c r="E160" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F160" s="4">
         <v>0</v>
       </c>
       <c r="G160" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H160" s="4">
         <v>0</v>
@@ -4968,14 +4968,14 @@
       <c r="D161" s="4"/>
       <c r="E161" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F161" s="4">
         <v>0</v>
       </c>
       <c r="G161" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H161" s="4">
         <v>0</v>
@@ -4996,14 +4996,14 @@
       <c r="D162" s="4"/>
       <c r="E162" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F162" s="4">
         <v>0</v>
       </c>
       <c r="G162" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H162" s="4">
         <v>0</v>
@@ -5024,14 +5024,14 @@
       <c r="D163" s="4"/>
       <c r="E163" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F163" s="4">
         <v>0</v>
       </c>
       <c r="G163" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H163" s="4">
         <v>0</v>
@@ -5052,14 +5052,14 @@
       <c r="D164" s="4"/>
       <c r="E164" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F164" s="4">
         <v>0</v>
       </c>
       <c r="G164" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H164" s="4">
         <v>0</v>
@@ -5080,14 +5080,14 @@
       <c r="D165" s="4"/>
       <c r="E165" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F165" s="4">
         <v>0</v>
       </c>
       <c r="G165" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H165" s="4">
         <v>0</v>
@@ -5108,14 +5108,14 @@
       <c r="D166" s="4"/>
       <c r="E166" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F166" s="4">
         <v>0</v>
       </c>
       <c r="G166" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H166" s="4">
         <v>0</v>
@@ -5136,14 +5136,14 @@
       <c r="D167" s="4"/>
       <c r="E167" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F167" s="4">
         <v>0</v>
       </c>
       <c r="G167" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H167" s="4">
         <v>0</v>
@@ -5164,14 +5164,14 @@
       <c r="D168" s="4"/>
       <c r="E168" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F168" s="4">
         <v>0</v>
       </c>
       <c r="G168" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H168" s="4">
         <v>0</v>
@@ -5192,14 +5192,14 @@
       <c r="D169" s="4"/>
       <c r="E169" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F169" s="4">
         <v>0</v>
       </c>
       <c r="G169" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H169" s="4">
         <v>0</v>
@@ -5220,14 +5220,14 @@
       <c r="D170" s="4"/>
       <c r="E170" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F170" s="4">
         <v>0</v>
       </c>
       <c r="G170" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H170" s="4">
         <v>0</v>
@@ -5248,14 +5248,14 @@
       <c r="D171" s="4"/>
       <c r="E171" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F171" s="4">
         <v>0</v>
       </c>
       <c r="G171" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H171" s="4">
         <v>0</v>
@@ -5276,14 +5276,14 @@
       <c r="D172" s="4"/>
       <c r="E172" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F172" s="4">
         <v>0</v>
       </c>
       <c r="G172" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H172" s="4">
         <v>0</v>
@@ -5304,14 +5304,14 @@
       <c r="D173" s="4"/>
       <c r="E173" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F173" s="4">
         <v>0</v>
       </c>
       <c r="G173" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H173" s="4">
         <v>0</v>
@@ -5332,14 +5332,14 @@
       <c r="D174" s="4"/>
       <c r="E174" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F174" s="4">
         <v>0</v>
       </c>
       <c r="G174" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H174" s="4">
         <v>0</v>
@@ -5360,14 +5360,14 @@
       <c r="D175" s="4"/>
       <c r="E175" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F175" s="4">
         <v>0</v>
       </c>
       <c r="G175" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H175" s="4">
         <v>0</v>
@@ -5388,14 +5388,14 @@
       <c r="D176" s="4"/>
       <c r="E176" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F176" s="4">
         <v>0</v>
       </c>
       <c r="G176" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H176" s="4">
         <v>0</v>
@@ -5416,14 +5416,14 @@
       <c r="D177" s="4"/>
       <c r="E177" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F177" s="4">
         <v>0</v>
       </c>
       <c r="G177" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H177" s="4">
         <v>0</v>
@@ -5444,14 +5444,14 @@
       <c r="D178" s="4"/>
       <c r="E178" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F178" s="4">
         <v>0</v>
       </c>
       <c r="G178" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H178" s="4">
         <v>0</v>
@@ -5472,14 +5472,14 @@
       <c r="D179" s="4"/>
       <c r="E179" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F179" s="4">
         <v>0</v>
       </c>
       <c r="G179" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H179" s="4">
         <v>0</v>
@@ -5500,14 +5500,14 @@
       <c r="D180" s="4"/>
       <c r="E180" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F180" s="4">
         <v>0</v>
       </c>
       <c r="G180" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H180" s="4">
         <v>0</v>
@@ -5528,14 +5528,14 @@
       <c r="D181" s="4"/>
       <c r="E181" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F181" s="4">
         <v>0</v>
       </c>
       <c r="G181" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H181" s="4">
         <v>0</v>
@@ -5556,14 +5556,14 @@
       <c r="D182" s="4"/>
       <c r="E182" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F182" s="4">
         <v>0</v>
       </c>
       <c r="G182" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H182" s="4">
         <v>0</v>
@@ -5584,14 +5584,14 @@
       <c r="D183" s="4"/>
       <c r="E183" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F183" s="4">
         <v>0</v>
       </c>
       <c r="G183" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H183" s="4">
         <v>0</v>
@@ -5612,14 +5612,14 @@
       <c r="D184" s="4"/>
       <c r="E184" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F184" s="4">
         <v>0</v>
       </c>
       <c r="G184" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H184" s="4">
         <v>0</v>
@@ -5640,14 +5640,14 @@
       <c r="D185" s="4"/>
       <c r="E185" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F185" s="4">
         <v>0</v>
       </c>
       <c r="G185" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H185" s="4">
         <v>0</v>
@@ -5668,14 +5668,14 @@
       <c r="D186" s="4"/>
       <c r="E186" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F186" s="4">
         <v>0</v>
       </c>
       <c r="G186" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H186" s="4">
         <v>0</v>
@@ -5696,14 +5696,14 @@
       <c r="D187" s="4"/>
       <c r="E187" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F187" s="4">
         <v>0</v>
       </c>
       <c r="G187" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H187" s="4">
         <v>0</v>
@@ -5724,14 +5724,14 @@
       <c r="D188" s="4"/>
       <c r="E188" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F188" s="4">
         <v>0</v>
       </c>
       <c r="G188" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H188" s="4">
         <v>0</v>
@@ -5752,14 +5752,14 @@
       <c r="D189" s="4"/>
       <c r="E189" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F189" s="4">
         <v>0</v>
       </c>
       <c r="G189" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H189" s="4">
         <v>0</v>
@@ -5780,14 +5780,14 @@
       <c r="D190" s="4"/>
       <c r="E190" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F190" s="4">
         <v>0</v>
       </c>
       <c r="G190" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H190" s="4">
         <v>0</v>
@@ -5808,14 +5808,14 @@
       <c r="D191" s="4"/>
       <c r="E191" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F191" s="4">
         <v>0</v>
       </c>
       <c r="G191" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H191" s="4">
         <v>0</v>
@@ -5836,14 +5836,14 @@
       <c r="D192" s="4"/>
       <c r="E192" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F192" s="4">
         <v>0</v>
       </c>
       <c r="G192" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H192" s="4">
         <v>0</v>
@@ -5864,14 +5864,14 @@
       <c r="D193" s="4"/>
       <c r="E193" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F193" s="4">
         <v>0</v>
       </c>
       <c r="G193" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H193" s="4">
         <v>0</v>
@@ -5892,14 +5892,14 @@
       <c r="D194" s="4"/>
       <c r="E194" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F194" s="4">
         <v>0</v>
       </c>
       <c r="G194" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H194" s="4">
         <v>0</v>
@@ -5920,14 +5920,14 @@
       <c r="D195" s="4"/>
       <c r="E195" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F195" s="4">
         <v>0</v>
       </c>
       <c r="G195" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H195" s="4">
         <v>0</v>
@@ -5948,14 +5948,14 @@
       <c r="D196" s="4"/>
       <c r="E196" s="5">
         <f t="shared" ref="E196:E259" ca="1" si="18">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F196" s="4">
         <v>0</v>
       </c>
       <c r="G196" s="5">
         <f t="shared" ref="G196:G259" ca="1" si="19">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H196" s="4">
         <v>0</v>
@@ -5976,14 +5976,14 @@
       <c r="D197" s="4"/>
       <c r="E197" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F197" s="4">
         <v>0</v>
       </c>
       <c r="G197" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H197" s="4">
         <v>0</v>
@@ -6004,14 +6004,14 @@
       <c r="D198" s="4"/>
       <c r="E198" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F198" s="4">
         <v>0</v>
       </c>
       <c r="G198" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H198" s="4">
         <v>0</v>
@@ -6032,14 +6032,14 @@
       <c r="D199" s="4"/>
       <c r="E199" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F199" s="4">
         <v>0</v>
       </c>
       <c r="G199" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H199" s="4">
         <v>0</v>
@@ -6060,14 +6060,14 @@
       <c r="D200" s="4"/>
       <c r="E200" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F200" s="4">
         <v>0</v>
       </c>
       <c r="G200" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H200" s="4">
         <v>0</v>
@@ -6088,14 +6088,14 @@
       <c r="D201" s="4"/>
       <c r="E201" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F201" s="4">
         <v>0</v>
       </c>
       <c r="G201" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H201" s="4">
         <v>0</v>
@@ -6116,14 +6116,14 @@
       <c r="D202" s="4"/>
       <c r="E202" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F202" s="4">
         <v>0</v>
       </c>
       <c r="G202" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H202" s="4">
         <v>0</v>
@@ -6144,14 +6144,14 @@
       <c r="D203" s="4"/>
       <c r="E203" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F203" s="4">
         <v>0</v>
       </c>
       <c r="G203" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H203" s="4">
         <v>0</v>
@@ -6172,14 +6172,14 @@
       <c r="D204" s="4"/>
       <c r="E204" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F204" s="4">
         <v>0</v>
       </c>
       <c r="G204" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H204" s="4">
         <v>0</v>
@@ -6200,14 +6200,14 @@
       <c r="D205" s="4"/>
       <c r="E205" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F205" s="4">
         <v>0</v>
       </c>
       <c r="G205" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H205" s="4">
         <v>0</v>
@@ -6228,14 +6228,14 @@
       <c r="D206" s="4"/>
       <c r="E206" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F206" s="4">
         <v>0</v>
       </c>
       <c r="G206" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H206" s="4">
         <v>0</v>
@@ -6256,14 +6256,14 @@
       <c r="D207" s="4"/>
       <c r="E207" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F207" s="4">
         <v>0</v>
       </c>
       <c r="G207" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H207" s="4">
         <v>0</v>
@@ -6284,14 +6284,14 @@
       <c r="D208" s="4"/>
       <c r="E208" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F208" s="4">
         <v>0</v>
       </c>
       <c r="G208" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H208" s="4">
         <v>0</v>
@@ -6312,14 +6312,14 @@
       <c r="D209" s="4"/>
       <c r="E209" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F209" s="4">
         <v>0</v>
       </c>
       <c r="G209" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H209" s="4">
         <v>0</v>
@@ -6340,14 +6340,14 @@
       <c r="D210" s="4"/>
       <c r="E210" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F210" s="4">
         <v>0</v>
       </c>
       <c r="G210" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H210" s="4">
         <v>0</v>
@@ -6368,14 +6368,14 @@
       <c r="D211" s="4"/>
       <c r="E211" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F211" s="4">
         <v>0</v>
       </c>
       <c r="G211" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H211" s="4">
         <v>0</v>
@@ -6396,14 +6396,14 @@
       <c r="D212" s="4"/>
       <c r="E212" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F212" s="4">
         <v>0</v>
       </c>
       <c r="G212" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H212" s="4">
         <v>0</v>
@@ -6424,14 +6424,14 @@
       <c r="D213" s="4"/>
       <c r="E213" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F213" s="4">
         <v>0</v>
       </c>
       <c r="G213" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H213" s="4">
         <v>0</v>
@@ -6452,14 +6452,14 @@
       <c r="D214" s="4"/>
       <c r="E214" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F214" s="4">
         <v>0</v>
       </c>
       <c r="G214" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H214" s="4">
         <v>0</v>
@@ -6480,14 +6480,14 @@
       <c r="D215" s="4"/>
       <c r="E215" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F215" s="4">
         <v>0</v>
       </c>
       <c r="G215" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H215" s="4">
         <v>0</v>
@@ -6508,14 +6508,14 @@
       <c r="D216" s="4"/>
       <c r="E216" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F216" s="4">
         <v>0</v>
       </c>
       <c r="G216" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H216" s="4">
         <v>0</v>
@@ -6536,14 +6536,14 @@
       <c r="D217" s="4"/>
       <c r="E217" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F217" s="4">
         <v>0</v>
       </c>
       <c r="G217" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H217" s="4">
         <v>0</v>
@@ -6564,14 +6564,14 @@
       <c r="D218" s="4"/>
       <c r="E218" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F218" s="4">
         <v>0</v>
       </c>
       <c r="G218" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H218" s="4">
         <v>0</v>
@@ -6592,14 +6592,14 @@
       <c r="D219" s="4"/>
       <c r="E219" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F219" s="4">
         <v>0</v>
       </c>
       <c r="G219" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H219" s="4">
         <v>0</v>
@@ -6620,14 +6620,14 @@
       <c r="D220" s="4"/>
       <c r="E220" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F220" s="4">
         <v>0</v>
       </c>
       <c r="G220" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H220" s="4">
         <v>0</v>
@@ -6648,14 +6648,14 @@
       <c r="D221" s="4"/>
       <c r="E221" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F221" s="4">
         <v>0</v>
       </c>
       <c r="G221" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H221" s="4">
         <v>0</v>
@@ -6676,14 +6676,14 @@
       <c r="D222" s="4"/>
       <c r="E222" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F222" s="4">
         <v>0</v>
       </c>
       <c r="G222" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H222" s="4">
         <v>0</v>
@@ -6704,14 +6704,14 @@
       <c r="D223" s="4"/>
       <c r="E223" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F223" s="4">
         <v>0</v>
       </c>
       <c r="G223" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H223" s="4">
         <v>0</v>
@@ -6732,14 +6732,14 @@
       <c r="D224" s="4"/>
       <c r="E224" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F224" s="4">
         <v>0</v>
       </c>
       <c r="G224" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H224" s="4">
         <v>0</v>
@@ -6760,14 +6760,14 @@
       <c r="D225" s="4"/>
       <c r="E225" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F225" s="4">
         <v>0</v>
       </c>
       <c r="G225" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H225" s="4">
         <v>0</v>
@@ -6788,14 +6788,14 @@
       <c r="D226" s="4"/>
       <c r="E226" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F226" s="4">
         <v>0</v>
       </c>
       <c r="G226" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H226" s="4">
         <v>0</v>
@@ -6816,14 +6816,14 @@
       <c r="D227" s="4"/>
       <c r="E227" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F227" s="4">
         <v>0</v>
       </c>
       <c r="G227" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H227" s="4">
         <v>0</v>
@@ -6844,14 +6844,14 @@
       <c r="D228" s="4"/>
       <c r="E228" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F228" s="4">
         <v>0</v>
       </c>
       <c r="G228" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H228" s="4">
         <v>0</v>
@@ -6872,14 +6872,14 @@
       <c r="D229" s="4"/>
       <c r="E229" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F229" s="4">
         <v>0</v>
       </c>
       <c r="G229" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H229" s="4">
         <v>0</v>
@@ -6900,14 +6900,14 @@
       <c r="D230" s="4"/>
       <c r="E230" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F230" s="4">
         <v>0</v>
       </c>
       <c r="G230" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H230" s="4">
         <v>0</v>
@@ -6928,14 +6928,14 @@
       <c r="D231" s="4"/>
       <c r="E231" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F231" s="4">
         <v>0</v>
       </c>
       <c r="G231" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H231" s="4">
         <v>0</v>
@@ -6956,14 +6956,14 @@
       <c r="D232" s="4"/>
       <c r="E232" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F232" s="4">
         <v>0</v>
       </c>
       <c r="G232" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H232" s="4">
         <v>0</v>
@@ -6984,14 +6984,14 @@
       <c r="D233" s="4"/>
       <c r="E233" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F233" s="4">
         <v>0</v>
       </c>
       <c r="G233" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H233" s="4">
         <v>0</v>
@@ -7012,14 +7012,14 @@
       <c r="D234" s="4"/>
       <c r="E234" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F234" s="4">
         <v>0</v>
       </c>
       <c r="G234" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H234" s="4">
         <v>0</v>
@@ -7040,14 +7040,14 @@
       <c r="D235" s="4"/>
       <c r="E235" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F235" s="4">
         <v>0</v>
       </c>
       <c r="G235" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H235" s="4">
         <v>0</v>
@@ -7068,14 +7068,14 @@
       <c r="D236" s="4"/>
       <c r="E236" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F236" s="4">
         <v>0</v>
       </c>
       <c r="G236" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H236" s="4">
         <v>0</v>
@@ -7096,14 +7096,14 @@
       <c r="D237" s="4"/>
       <c r="E237" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F237" s="4">
         <v>0</v>
       </c>
       <c r="G237" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H237" s="4">
         <v>0</v>
@@ -7124,14 +7124,14 @@
       <c r="D238" s="4"/>
       <c r="E238" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F238" s="4">
         <v>0</v>
       </c>
       <c r="G238" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H238" s="4">
         <v>0</v>
@@ -7152,14 +7152,14 @@
       <c r="D239" s="4"/>
       <c r="E239" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F239" s="4">
         <v>0</v>
       </c>
       <c r="G239" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H239" s="4">
         <v>0</v>
@@ -7180,14 +7180,14 @@
       <c r="D240" s="4"/>
       <c r="E240" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F240" s="4">
         <v>0</v>
       </c>
       <c r="G240" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H240" s="4">
         <v>0</v>
@@ -7208,14 +7208,14 @@
       <c r="D241" s="4"/>
       <c r="E241" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F241" s="4">
         <v>0</v>
       </c>
       <c r="G241" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H241" s="4">
         <v>0</v>
@@ -7236,14 +7236,14 @@
       <c r="D242" s="4"/>
       <c r="E242" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F242" s="4">
         <v>0</v>
       </c>
       <c r="G242" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H242" s="4">
         <v>0</v>
@@ -7264,14 +7264,14 @@
       <c r="D243" s="4"/>
       <c r="E243" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F243" s="4">
         <v>0</v>
       </c>
       <c r="G243" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H243" s="4">
         <v>0</v>
@@ -7292,14 +7292,14 @@
       <c r="D244" s="4"/>
       <c r="E244" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F244" s="4">
         <v>0</v>
       </c>
       <c r="G244" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H244" s="4">
         <v>0</v>
@@ -7320,14 +7320,14 @@
       <c r="D245" s="4"/>
       <c r="E245" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F245" s="4">
         <v>0</v>
       </c>
       <c r="G245" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H245" s="4">
         <v>0</v>
@@ -7348,14 +7348,14 @@
       <c r="D246" s="4"/>
       <c r="E246" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F246" s="4">
         <v>0</v>
       </c>
       <c r="G246" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H246" s="4">
         <v>0</v>
@@ -7376,14 +7376,14 @@
       <c r="D247" s="4"/>
       <c r="E247" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F247" s="4">
         <v>0</v>
       </c>
       <c r="G247" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H247" s="4">
         <v>0</v>
@@ -7404,14 +7404,14 @@
       <c r="D248" s="4"/>
       <c r="E248" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F248" s="4">
         <v>0</v>
       </c>
       <c r="G248" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H248" s="4">
         <v>0</v>
@@ -7432,14 +7432,14 @@
       <c r="D249" s="4"/>
       <c r="E249" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F249" s="4">
         <v>0</v>
       </c>
       <c r="G249" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H249" s="4">
         <v>0</v>
@@ -7460,14 +7460,14 @@
       <c r="D250" s="4"/>
       <c r="E250" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F250" s="4">
         <v>0</v>
       </c>
       <c r="G250" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H250" s="4">
         <v>0</v>
@@ -7488,14 +7488,14 @@
       <c r="D251" s="4"/>
       <c r="E251" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F251" s="4">
         <v>0</v>
       </c>
       <c r="G251" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H251" s="4">
         <v>0</v>
@@ -7516,14 +7516,14 @@
       <c r="D252" s="4"/>
       <c r="E252" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F252" s="4">
         <v>0</v>
       </c>
       <c r="G252" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H252" s="4">
         <v>0</v>
@@ -7544,14 +7544,14 @@
       <c r="D253" s="4"/>
       <c r="E253" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F253" s="4">
         <v>0</v>
       </c>
       <c r="G253" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H253" s="4">
         <v>0</v>
@@ -7572,14 +7572,14 @@
       <c r="D254" s="4"/>
       <c r="E254" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F254" s="4">
         <v>0</v>
       </c>
       <c r="G254" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H254" s="4">
         <v>0</v>
@@ -7600,14 +7600,14 @@
       <c r="D255" s="4"/>
       <c r="E255" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F255" s="4">
         <v>0</v>
       </c>
       <c r="G255" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H255" s="4">
         <v>0</v>
@@ -7628,14 +7628,14 @@
       <c r="D256" s="4"/>
       <c r="E256" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F256" s="4">
         <v>0</v>
       </c>
       <c r="G256" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H256" s="4">
         <v>0</v>
@@ -7656,14 +7656,14 @@
       <c r="D257" s="4"/>
       <c r="E257" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F257" s="4">
         <v>0</v>
       </c>
       <c r="G257" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H257" s="4">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       <c r="D258" s="4"/>
       <c r="E258" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F258" s="4">
         <v>0</v>
       </c>
       <c r="G258" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H258" s="4">
         <v>0</v>
@@ -7712,14 +7712,14 @@
       <c r="D259" s="4"/>
       <c r="E259" s="5">
         <f t="shared" ca="1" si="18"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F259" s="4">
         <v>0</v>
       </c>
       <c r="G259" s="5">
         <f t="shared" ca="1" si="19"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H259" s="4">
         <v>0</v>
@@ -7740,14 +7740,14 @@
       <c r="D260" s="4"/>
       <c r="E260" s="5">
         <f t="shared" ref="E260:E323" ca="1" si="22">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F260" s="4">
         <v>0</v>
       </c>
       <c r="G260" s="5">
         <f t="shared" ref="G260:G323" ca="1" si="23">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H260" s="4">
         <v>0</v>
@@ -7768,14 +7768,14 @@
       <c r="D261" s="4"/>
       <c r="E261" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F261" s="4">
         <v>0</v>
       </c>
       <c r="G261" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H261" s="4">
         <v>0</v>
@@ -7796,14 +7796,14 @@
       <c r="D262" s="4"/>
       <c r="E262" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F262" s="4">
         <v>0</v>
       </c>
       <c r="G262" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H262" s="4">
         <v>0</v>
@@ -7824,14 +7824,14 @@
       <c r="D263" s="4"/>
       <c r="E263" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F263" s="4">
         <v>0</v>
       </c>
       <c r="G263" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H263" s="4">
         <v>0</v>
@@ -7852,14 +7852,14 @@
       <c r="D264" s="4"/>
       <c r="E264" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F264" s="4">
         <v>0</v>
       </c>
       <c r="G264" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H264" s="4">
         <v>0</v>
@@ -7880,14 +7880,14 @@
       <c r="D265" s="4"/>
       <c r="E265" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F265" s="4">
         <v>0</v>
       </c>
       <c r="G265" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H265" s="4">
         <v>0</v>
@@ -7908,14 +7908,14 @@
       <c r="D266" s="4"/>
       <c r="E266" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F266" s="4">
         <v>0</v>
       </c>
       <c r="G266" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H266" s="4">
         <v>0</v>
@@ -7936,14 +7936,14 @@
       <c r="D267" s="4"/>
       <c r="E267" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F267" s="4">
         <v>0</v>
       </c>
       <c r="G267" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H267" s="4">
         <v>0</v>
@@ -7964,14 +7964,14 @@
       <c r="D268" s="4"/>
       <c r="E268" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F268" s="4">
         <v>0</v>
       </c>
       <c r="G268" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H268" s="4">
         <v>0</v>
@@ -7992,14 +7992,14 @@
       <c r="D269" s="4"/>
       <c r="E269" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F269" s="4">
         <v>0</v>
       </c>
       <c r="G269" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H269" s="4">
         <v>0</v>
@@ -8020,14 +8020,14 @@
       <c r="D270" s="4"/>
       <c r="E270" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F270" s="4">
         <v>0</v>
       </c>
       <c r="G270" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H270" s="4">
         <v>0</v>
@@ -8048,14 +8048,14 @@
       <c r="D271" s="4"/>
       <c r="E271" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F271" s="4">
         <v>0</v>
       </c>
       <c r="G271" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H271" s="4">
         <v>0</v>
@@ -8076,14 +8076,14 @@
       <c r="D272" s="4"/>
       <c r="E272" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F272" s="4">
         <v>0</v>
       </c>
       <c r="G272" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H272" s="4">
         <v>0</v>
@@ -8104,14 +8104,14 @@
       <c r="D273" s="4"/>
       <c r="E273" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F273" s="4">
         <v>0</v>
       </c>
       <c r="G273" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H273" s="4">
         <v>0</v>
@@ -8132,14 +8132,14 @@
       <c r="D274" s="4"/>
       <c r="E274" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F274" s="4">
         <v>0</v>
       </c>
       <c r="G274" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H274" s="4">
         <v>0</v>
@@ -8160,14 +8160,14 @@
       <c r="D275" s="4"/>
       <c r="E275" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F275" s="4">
         <v>0</v>
       </c>
       <c r="G275" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H275" s="4">
         <v>0</v>
@@ -8188,14 +8188,14 @@
       <c r="D276" s="4"/>
       <c r="E276" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F276" s="4">
         <v>0</v>
       </c>
       <c r="G276" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H276" s="4">
         <v>0</v>
@@ -8216,14 +8216,14 @@
       <c r="D277" s="4"/>
       <c r="E277" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F277" s="4">
         <v>0</v>
       </c>
       <c r="G277" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H277" s="4">
         <v>0</v>
@@ -8244,14 +8244,14 @@
       <c r="D278" s="4"/>
       <c r="E278" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F278" s="4">
         <v>0</v>
       </c>
       <c r="G278" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H278" s="4">
         <v>0</v>
@@ -8272,14 +8272,14 @@
       <c r="D279" s="4"/>
       <c r="E279" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F279" s="4">
         <v>0</v>
       </c>
       <c r="G279" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H279" s="4">
         <v>0</v>
@@ -8300,14 +8300,14 @@
       <c r="D280" s="4"/>
       <c r="E280" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F280" s="4">
         <v>0</v>
       </c>
       <c r="G280" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H280" s="4">
         <v>0</v>
@@ -8328,14 +8328,14 @@
       <c r="D281" s="4"/>
       <c r="E281" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F281" s="4">
         <v>0</v>
       </c>
       <c r="G281" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H281" s="4">
         <v>0</v>
@@ -8356,14 +8356,14 @@
       <c r="D282" s="4"/>
       <c r="E282" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F282" s="4">
         <v>0</v>
       </c>
       <c r="G282" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H282" s="4">
         <v>0</v>
@@ -8384,14 +8384,14 @@
       <c r="D283" s="4"/>
       <c r="E283" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F283" s="4">
         <v>0</v>
       </c>
       <c r="G283" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H283" s="4">
         <v>0</v>
@@ -8412,14 +8412,14 @@
       <c r="D284" s="4"/>
       <c r="E284" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F284" s="4">
         <v>0</v>
       </c>
       <c r="G284" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H284" s="4">
         <v>0</v>
@@ -8440,14 +8440,14 @@
       <c r="D285" s="4"/>
       <c r="E285" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F285" s="4">
         <v>0</v>
       </c>
       <c r="G285" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H285" s="4">
         <v>0</v>
@@ -8468,14 +8468,14 @@
       <c r="D286" s="4"/>
       <c r="E286" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F286" s="4">
         <v>0</v>
       </c>
       <c r="G286" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H286" s="4">
         <v>0</v>
@@ -8496,14 +8496,14 @@
       <c r="D287" s="4"/>
       <c r="E287" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F287" s="4">
         <v>0</v>
       </c>
       <c r="G287" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H287" s="4">
         <v>0</v>
@@ -8524,14 +8524,14 @@
       <c r="D288" s="4"/>
       <c r="E288" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F288" s="4">
         <v>0</v>
       </c>
       <c r="G288" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H288" s="4">
         <v>0</v>
@@ -8552,14 +8552,14 @@
       <c r="D289" s="4"/>
       <c r="E289" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F289" s="4">
         <v>0</v>
       </c>
       <c r="G289" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H289" s="4">
         <v>0</v>
@@ -8580,14 +8580,14 @@
       <c r="D290" s="4"/>
       <c r="E290" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F290" s="4">
         <v>0</v>
       </c>
       <c r="G290" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H290" s="4">
         <v>0</v>
@@ -8608,14 +8608,14 @@
       <c r="D291" s="4"/>
       <c r="E291" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F291" s="4">
         <v>0</v>
       </c>
       <c r="G291" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H291" s="4">
         <v>0</v>
@@ -8636,14 +8636,14 @@
       <c r="D292" s="4"/>
       <c r="E292" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F292" s="4">
         <v>0</v>
       </c>
       <c r="G292" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H292" s="4">
         <v>0</v>
@@ -8664,14 +8664,14 @@
       <c r="D293" s="4"/>
       <c r="E293" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F293" s="4">
         <v>0</v>
       </c>
       <c r="G293" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H293" s="4">
         <v>0</v>
@@ -8692,14 +8692,14 @@
       <c r="D294" s="4"/>
       <c r="E294" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F294" s="4">
         <v>0</v>
       </c>
       <c r="G294" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H294" s="4">
         <v>0</v>
@@ -8720,14 +8720,14 @@
       <c r="D295" s="4"/>
       <c r="E295" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F295" s="4">
         <v>0</v>
       </c>
       <c r="G295" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H295" s="4">
         <v>0</v>
@@ -8748,14 +8748,14 @@
       <c r="D296" s="4"/>
       <c r="E296" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F296" s="4">
         <v>0</v>
       </c>
       <c r="G296" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H296" s="4">
         <v>0</v>
@@ -8776,14 +8776,14 @@
       <c r="D297" s="4"/>
       <c r="E297" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F297" s="4">
         <v>0</v>
       </c>
       <c r="G297" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H297" s="4">
         <v>0</v>
@@ -8804,14 +8804,14 @@
       <c r="D298" s="4"/>
       <c r="E298" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F298" s="4">
         <v>0</v>
       </c>
       <c r="G298" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H298" s="4">
         <v>0</v>
@@ -8832,14 +8832,14 @@
       <c r="D299" s="4"/>
       <c r="E299" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F299" s="4">
         <v>0</v>
       </c>
       <c r="G299" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H299" s="4">
         <v>0</v>
@@ -8860,14 +8860,14 @@
       <c r="D300" s="4"/>
       <c r="E300" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F300" s="4">
         <v>0</v>
       </c>
       <c r="G300" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H300" s="4">
         <v>0</v>
@@ -8888,14 +8888,14 @@
       <c r="D301" s="4"/>
       <c r="E301" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F301" s="4">
         <v>0</v>
       </c>
       <c r="G301" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H301" s="4">
         <v>0</v>
@@ -8916,14 +8916,14 @@
       <c r="D302" s="4"/>
       <c r="E302" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F302" s="4">
         <v>0</v>
       </c>
       <c r="G302" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H302" s="4">
         <v>0</v>
@@ -8944,14 +8944,14 @@
       <c r="D303" s="4"/>
       <c r="E303" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F303" s="4">
         <v>0</v>
       </c>
       <c r="G303" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H303" s="4">
         <v>0</v>
@@ -8972,14 +8972,14 @@
       <c r="D304" s="4"/>
       <c r="E304" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F304" s="4">
         <v>0</v>
       </c>
       <c r="G304" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H304" s="4">
         <v>0</v>
@@ -9000,14 +9000,14 @@
       <c r="D305" s="4"/>
       <c r="E305" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F305" s="4">
         <v>0</v>
       </c>
       <c r="G305" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H305" s="4">
         <v>0</v>
@@ -9028,14 +9028,14 @@
       <c r="D306" s="4"/>
       <c r="E306" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F306" s="4">
         <v>0</v>
       </c>
       <c r="G306" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H306" s="4">
         <v>0</v>
@@ -9056,14 +9056,14 @@
       <c r="D307" s="4"/>
       <c r="E307" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F307" s="4">
         <v>0</v>
       </c>
       <c r="G307" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H307" s="4">
         <v>0</v>
@@ -9084,14 +9084,14 @@
       <c r="D308" s="4"/>
       <c r="E308" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F308" s="4">
         <v>0</v>
       </c>
       <c r="G308" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H308" s="4">
         <v>0</v>
@@ -9112,14 +9112,14 @@
       <c r="D309" s="4"/>
       <c r="E309" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F309" s="4">
         <v>0</v>
       </c>
       <c r="G309" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H309" s="4">
         <v>0</v>
@@ -9140,14 +9140,14 @@
       <c r="D310" s="4"/>
       <c r="E310" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F310" s="4">
         <v>0</v>
       </c>
       <c r="G310" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H310" s="4">
         <v>0</v>
@@ -9168,14 +9168,14 @@
       <c r="D311" s="4"/>
       <c r="E311" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F311" s="4">
         <v>0</v>
       </c>
       <c r="G311" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H311" s="4">
         <v>0</v>
@@ -9196,14 +9196,14 @@
       <c r="D312" s="4"/>
       <c r="E312" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F312" s="4">
         <v>0</v>
       </c>
       <c r="G312" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H312" s="4">
         <v>0</v>
@@ -9224,14 +9224,14 @@
       <c r="D313" s="4"/>
       <c r="E313" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F313" s="4">
         <v>0</v>
       </c>
       <c r="G313" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H313" s="4">
         <v>0</v>
@@ -9252,14 +9252,14 @@
       <c r="D314" s="4"/>
       <c r="E314" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F314" s="4">
         <v>0</v>
       </c>
       <c r="G314" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H314" s="4">
         <v>0</v>
@@ -9280,14 +9280,14 @@
       <c r="D315" s="4"/>
       <c r="E315" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F315" s="4">
         <v>0</v>
       </c>
       <c r="G315" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H315" s="4">
         <v>0</v>
@@ -9308,14 +9308,14 @@
       <c r="D316" s="4"/>
       <c r="E316" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F316" s="4">
         <v>0</v>
       </c>
       <c r="G316" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H316" s="4">
         <v>0</v>
@@ -9336,14 +9336,14 @@
       <c r="D317" s="4"/>
       <c r="E317" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F317" s="4">
         <v>0</v>
       </c>
       <c r="G317" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H317" s="4">
         <v>0</v>
@@ -9364,14 +9364,14 @@
       <c r="D318" s="4"/>
       <c r="E318" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F318" s="4">
         <v>0</v>
       </c>
       <c r="G318" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H318" s="4">
         <v>0</v>
@@ -9392,14 +9392,14 @@
       <c r="D319" s="4"/>
       <c r="E319" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F319" s="4">
         <v>0</v>
       </c>
       <c r="G319" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H319" s="4">
         <v>0</v>
@@ -9420,14 +9420,14 @@
       <c r="D320" s="4"/>
       <c r="E320" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F320" s="4">
         <v>0</v>
       </c>
       <c r="G320" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H320" s="4">
         <v>0</v>
@@ -9448,14 +9448,14 @@
       <c r="D321" s="4"/>
       <c r="E321" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F321" s="4">
         <v>0</v>
       </c>
       <c r="G321" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H321" s="4">
         <v>0</v>
@@ -9476,14 +9476,14 @@
       <c r="D322" s="4"/>
       <c r="E322" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F322" s="4">
         <v>0</v>
       </c>
       <c r="G322" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H322" s="4">
         <v>0</v>
@@ -9504,14 +9504,14 @@
       <c r="D323" s="4"/>
       <c r="E323" s="5">
         <f t="shared" ca="1" si="22"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F323" s="4">
         <v>0</v>
       </c>
       <c r="G323" s="5">
         <f t="shared" ca="1" si="23"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H323" s="4">
         <v>0</v>
@@ -9532,14 +9532,14 @@
       <c r="D324" s="4"/>
       <c r="E324" s="5">
         <f t="shared" ref="E324:E367" ca="1" si="26">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F324" s="4">
         <v>0</v>
       </c>
       <c r="G324" s="5">
         <f t="shared" ref="G324:G367" ca="1" si="27">NOW()</f>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H324" s="4">
         <v>0</v>
@@ -9560,14 +9560,14 @@
       <c r="D325" s="4"/>
       <c r="E325" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F325" s="4">
         <v>0</v>
       </c>
       <c r="G325" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H325" s="4">
         <v>0</v>
@@ -9588,14 +9588,14 @@
       <c r="D326" s="4"/>
       <c r="E326" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F326" s="4">
         <v>0</v>
       </c>
       <c r="G326" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H326" s="4">
         <v>0</v>
@@ -9616,14 +9616,14 @@
       <c r="D327" s="4"/>
       <c r="E327" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F327" s="4">
         <v>0</v>
       </c>
       <c r="G327" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H327" s="4">
         <v>0</v>
@@ -9644,14 +9644,14 @@
       <c r="D328" s="4"/>
       <c r="E328" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F328" s="4">
         <v>0</v>
       </c>
       <c r="G328" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H328" s="4">
         <v>0</v>
@@ -9672,14 +9672,14 @@
       <c r="D329" s="4"/>
       <c r="E329" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F329" s="4">
         <v>0</v>
       </c>
       <c r="G329" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H329" s="4">
         <v>0</v>
@@ -9700,14 +9700,14 @@
       <c r="D330" s="4"/>
       <c r="E330" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F330" s="4">
         <v>0</v>
       </c>
       <c r="G330" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H330" s="4">
         <v>0</v>
@@ -9728,14 +9728,14 @@
       <c r="D331" s="4"/>
       <c r="E331" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F331" s="4">
         <v>0</v>
       </c>
       <c r="G331" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H331" s="4">
         <v>0</v>
@@ -9756,14 +9756,14 @@
       <c r="D332" s="4"/>
       <c r="E332" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F332" s="4">
         <v>0</v>
       </c>
       <c r="G332" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H332" s="4">
         <v>0</v>
@@ -9784,14 +9784,14 @@
       <c r="D333" s="4"/>
       <c r="E333" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F333" s="4">
         <v>0</v>
       </c>
       <c r="G333" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H333" s="4">
         <v>0</v>
@@ -9812,14 +9812,14 @@
       <c r="D334" s="4"/>
       <c r="E334" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F334" s="4">
         <v>0</v>
       </c>
       <c r="G334" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H334" s="4">
         <v>0</v>
@@ -9840,14 +9840,14 @@
       <c r="D335" s="4"/>
       <c r="E335" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F335" s="4">
         <v>0</v>
       </c>
       <c r="G335" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H335" s="4">
         <v>0</v>
@@ -9868,14 +9868,14 @@
       <c r="D336" s="4"/>
       <c r="E336" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F336" s="4">
         <v>0</v>
       </c>
       <c r="G336" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H336" s="4">
         <v>0</v>
@@ -9896,14 +9896,14 @@
       <c r="D337" s="4"/>
       <c r="E337" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F337" s="4">
         <v>0</v>
       </c>
       <c r="G337" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H337" s="4">
         <v>0</v>
@@ -9924,14 +9924,14 @@
       <c r="D338" s="4"/>
       <c r="E338" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F338" s="4">
         <v>0</v>
       </c>
       <c r="G338" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H338" s="4">
         <v>0</v>
@@ -9952,14 +9952,14 @@
       <c r="D339" s="4"/>
       <c r="E339" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F339" s="4">
         <v>0</v>
       </c>
       <c r="G339" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H339" s="4">
         <v>0</v>
@@ -9980,14 +9980,14 @@
       <c r="D340" s="4"/>
       <c r="E340" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F340" s="4">
         <v>0</v>
       </c>
       <c r="G340" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H340" s="4">
         <v>0</v>
@@ -10008,14 +10008,14 @@
       <c r="D341" s="4"/>
       <c r="E341" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F341" s="4">
         <v>0</v>
       </c>
       <c r="G341" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H341" s="4">
         <v>0</v>
@@ -10036,14 +10036,14 @@
       <c r="D342" s="4"/>
       <c r="E342" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F342" s="4">
         <v>0</v>
       </c>
       <c r="G342" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H342" s="4">
         <v>0</v>
@@ -10064,14 +10064,14 @@
       <c r="D343" s="4"/>
       <c r="E343" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F343" s="4">
         <v>0</v>
       </c>
       <c r="G343" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H343" s="4">
         <v>0</v>
@@ -10092,14 +10092,14 @@
       <c r="D344" s="4"/>
       <c r="E344" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F344" s="4">
         <v>0</v>
       </c>
       <c r="G344" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H344" s="4">
         <v>0</v>
@@ -10120,14 +10120,14 @@
       <c r="D345" s="4"/>
       <c r="E345" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F345" s="4">
         <v>0</v>
       </c>
       <c r="G345" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H345" s="4">
         <v>0</v>
@@ -10148,14 +10148,14 @@
       <c r="D346" s="4"/>
       <c r="E346" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F346" s="4">
         <v>0</v>
       </c>
       <c r="G346" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H346" s="4">
         <v>0</v>
@@ -10176,14 +10176,14 @@
       <c r="D347" s="4"/>
       <c r="E347" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F347" s="4">
         <v>0</v>
       </c>
       <c r="G347" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H347" s="4">
         <v>0</v>
@@ -10204,14 +10204,14 @@
       <c r="D348" s="4"/>
       <c r="E348" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F348" s="4">
         <v>0</v>
       </c>
       <c r="G348" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H348" s="4">
         <v>0</v>
@@ -10232,14 +10232,14 @@
       <c r="D349" s="4"/>
       <c r="E349" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F349" s="4">
         <v>0</v>
       </c>
       <c r="G349" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H349" s="4">
         <v>0</v>
@@ -10260,14 +10260,14 @@
       <c r="D350" s="4"/>
       <c r="E350" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F350" s="4">
         <v>0</v>
       </c>
       <c r="G350" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H350" s="4">
         <v>0</v>
@@ -10288,14 +10288,14 @@
       <c r="D351" s="4"/>
       <c r="E351" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F351" s="4">
         <v>0</v>
       </c>
       <c r="G351" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H351" s="4">
         <v>0</v>
@@ -10316,14 +10316,14 @@
       <c r="D352" s="4"/>
       <c r="E352" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F352" s="4">
         <v>0</v>
       </c>
       <c r="G352" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H352" s="4">
         <v>0</v>
@@ -10344,14 +10344,14 @@
       <c r="D353" s="4"/>
       <c r="E353" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F353" s="4">
         <v>0</v>
       </c>
       <c r="G353" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H353" s="4">
         <v>0</v>
@@ -10372,14 +10372,14 @@
       <c r="D354" s="4"/>
       <c r="E354" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F354" s="4">
         <v>0</v>
       </c>
       <c r="G354" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H354" s="4">
         <v>0</v>
@@ -10400,14 +10400,14 @@
       <c r="D355" s="4"/>
       <c r="E355" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F355" s="4">
         <v>0</v>
       </c>
       <c r="G355" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H355" s="4">
         <v>0</v>
@@ -10428,14 +10428,14 @@
       <c r="D356" s="4"/>
       <c r="E356" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F356" s="4">
         <v>0</v>
       </c>
       <c r="G356" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H356" s="4">
         <v>0</v>
@@ -10456,14 +10456,14 @@
       <c r="D357" s="4"/>
       <c r="E357" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F357" s="4">
         <v>0</v>
       </c>
       <c r="G357" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H357" s="4">
         <v>0</v>
@@ -10484,14 +10484,14 @@
       <c r="D358" s="4"/>
       <c r="E358" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F358" s="4">
         <v>0</v>
       </c>
       <c r="G358" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H358" s="4">
         <v>0</v>
@@ -10512,14 +10512,14 @@
       <c r="D359" s="4"/>
       <c r="E359" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F359" s="4">
         <v>0</v>
       </c>
       <c r="G359" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H359" s="4">
         <v>0</v>
@@ -10540,14 +10540,14 @@
       <c r="D360" s="4"/>
       <c r="E360" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F360" s="4">
         <v>0</v>
       </c>
       <c r="G360" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H360" s="4">
         <v>0</v>
@@ -10568,14 +10568,14 @@
       <c r="D361" s="4"/>
       <c r="E361" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F361" s="4">
         <v>0</v>
       </c>
       <c r="G361" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H361" s="4">
         <v>0</v>
@@ -10596,14 +10596,14 @@
       <c r="D362" s="4"/>
       <c r="E362" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F362" s="4">
         <v>0</v>
       </c>
       <c r="G362" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H362" s="4">
         <v>0</v>
@@ -10624,14 +10624,14 @@
       <c r="D363" s="4"/>
       <c r="E363" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F363" s="4">
         <v>0</v>
       </c>
       <c r="G363" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H363" s="4">
         <v>0</v>
@@ -10652,14 +10652,14 @@
       <c r="D364" s="4"/>
       <c r="E364" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F364" s="4">
         <v>0</v>
       </c>
       <c r="G364" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H364" s="4">
         <v>0</v>
@@ -10680,14 +10680,14 @@
       <c r="D365" s="4"/>
       <c r="E365" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F365" s="4">
         <v>0</v>
       </c>
       <c r="G365" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H365" s="4">
         <v>0</v>
@@ -10708,14 +10708,14 @@
       <c r="D366" s="4"/>
       <c r="E366" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F366" s="4">
         <v>0</v>
       </c>
       <c r="G366" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H366" s="4">
         <v>0</v>
@@ -10736,14 +10736,14 @@
       <c r="D367" s="4"/>
       <c r="E367" s="5">
         <f t="shared" ca="1" si="26"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="F367" s="4">
         <v>0</v>
       </c>
       <c r="G367" s="5">
         <f t="shared" ca="1" si="27"/>
-        <v>46250.495241666664</v>
+        <v>46291.472132754629</v>
       </c>
       <c r="H367" s="4">
         <v>0</v>
